--- a/docs/reports/gold_templates/gold_SO_rotular.xlsx
+++ b/docs/reports/gold_templates/gold_SO_rotular.xlsx
@@ -498,17 +498,17 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Exercícios P2.pdf</t>
+          <t>02.05 Lâminas Segmentação.pdf</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>prova</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Exercícios P2</t>
+          <t>02.05 Lâminas Segmentação</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr"/>
@@ -521,17 +521,17 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Lista Exercícios P1.pdf</t>
+          <t>02.06 Lâminas Gerência de I O (Livro-texto).pdf</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>prova</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Lista Exercícios P1</t>
+          <t>02.06 Lâminas Gerência de I O (Livro texto)</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr"/>
@@ -544,17 +544,17 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Lista Exercícios P1 Gabarito.pdf</t>
+          <t>02.06 Lâminas Mecanismos de Interrupção.pdf</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>prova</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Lista Exercícios P1 Gabarito</t>
+          <t>02.06 Lâminas Mecanismos de Interrupção</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr"/>
@@ -567,17 +567,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Lista Exercícios P2.pdf</t>
+          <t>02.06 Lâminas Memória Virtual (Livro-texto).pdf</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>prova</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Lista Exercícios P2</t>
+          <t>02.06 Lâminas Memória Virtual (Livro texto)</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr"/>
@@ -590,17 +590,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Exercícios.pdf</t>
+          <t>07.04 Lâminas Comunicação e Sincronização.pdf</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>lista</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Exercícios</t>
+          <t>07.04 Lâminas Comunicação e Sincronização</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr"/>
@@ -613,17 +613,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>lista1_gab.pdf</t>
+          <t>09.04 Lâminas Semáforos.pdf</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>lista</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>lista1 gab</t>
+          <t>09.04 Lâminas Semáforos</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr"/>
@@ -636,17 +636,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>lista2.pdf</t>
+          <t>12.03 Processos.pdf</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>lista</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>lista2</t>
+          <t>12.03 Processos</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr"/>
@@ -659,17 +659,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Questões do ENADE sobre SISOP.pdf</t>
+          <t>12.05 Lâminas Gerência de Memória.pdf</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>lista</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Questões do ENADE sobre SISOP</t>
+          <t>12.05 Lâminas Gerência de Memória</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr"/>
@@ -682,17 +682,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>07.04 Exemplo threads em Java.zip</t>
+          <t>14 04 Troca de Mensagens.pdf</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>07.04 Exemplo threads em Java</t>
+          <t>14 04 Troca de Mensagens</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr"/>
@@ -705,17 +705,17 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Exemplo Criação de Processos no Unix Linux - filho.c</t>
+          <t>14.04 Lâminas IPC.pdf</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Exemplo Criação de Processos no Unix Linux filho</t>
+          <t>14.04 Lâminas IPC</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr"/>
@@ -728,17 +728,17 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Exemplo Criação de Processos no Unix Linux - teste01.c</t>
+          <t>14.04 Troca de Mensagens.pdf</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Exemplo Criação de Processos no Unix Linux teste01</t>
+          <t>14.04 Troca de Mensagens</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
@@ -751,17 +751,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Exemplo Criação de Processos no Unix Linux - teste02.c</t>
+          <t>17.03 Chamada de Sistema.pdf</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Exemplo Criação de Processos no Unix Linux teste02</t>
+          <t>17.03 Chamada de Sistema</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr"/>
@@ -774,17 +774,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Exemplo Criação de Processos no Unix Linux - teste03.c</t>
+          <t>19.03 Estruturas de Controle.pdf</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Exemplo Criação de Processos no Unix Linux teste03</t>
+          <t>19.03 Estruturas de Controle</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr"/>
@@ -797,17 +797,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Exemplo threads em C - exemplo1.c</t>
+          <t>21.05 Lâminas Paginação.pdf</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Exemplo threads em C exemplo1</t>
+          <t>21.05 Lâminas Paginação</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr"/>
@@ -820,17 +820,17 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Exemplo threads em C - exemplo2.c</t>
+          <t>23.06 Lâminas Gerência de Arquivos.pdf</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Exemplo threads em C exemplo2</t>
+          <t>23.06 Lâminas Gerência de Arquivos</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr"/>
@@ -843,17 +843,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Exemplo threads em C - exemplo3.c</t>
+          <t>23.06 Lâminas Lâminas Armazenamento em Massa.pdf</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>código</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Exemplo threads em C exemplo3</t>
+          <t>23.06 Lâminas Lâminas Armazenamento em Massa</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr"/>
@@ -866,17 +866,17 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Biblioteca em C - pthread.pdf</t>
+          <t>24.03 Escalonamento de Processos.pdf</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>artigo</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Biblioteca em C pthread</t>
+          <t>24.03 Escalonamento de Processos</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr"/>
@@ -889,17 +889,17 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Lâminas CS 4244 Internet Programming Sockets Programming.pdf</t>
+          <t>26.03 Algoritmos de Escalonamento.pdf</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>artigo</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Lâminas CS 4244 Internet Programming Sockets Programming</t>
+          <t>26.03 Algoritmos de Escalonamento</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr"/>
@@ -912,17 +912,17 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Lâminas Sockets (material alternativo em PT).pdf</t>
+          <t>31.03 Threads.pdf</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>artigo</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Lâminas Sockets (material alternativo em PT)</t>
+          <t>31.03 Threads</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr"/>
@@ -935,7 +935,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>02.05 Lâminas Segmentação.pdf</t>
+          <t>Apresentação da Disciplina.pdf</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>02.05 Lâminas Segmentação</t>
+          <t>Apresentação da Disciplina</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr"/>
@@ -958,7 +958,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>02.06 Lâminas Gerência de I O (Livro-texto).pdf</t>
+          <t>Biblioteca em C - pthread.pdf</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>02.06 Lâminas Gerência de I O (Livro texto)</t>
+          <t>Biblioteca em C pthread</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr"/>
@@ -981,7 +981,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>02.06 Lâminas Mecanismos de Interrupção.pdf</t>
+          <t>Definição e Histórico.pdf</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>02.06 Lâminas Mecanismos de Interrupção</t>
+          <t>Definição e Histórico</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>02.06 Lâminas Memória Virtual (Livro-texto).pdf</t>
+          <t>Exercícios.pdf</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>02.06 Lâminas Memória Virtual (Livro texto)</t>
+          <t>Exercícios</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>07.04 Lâminas Comunicação e Sincronização.pdf</t>
+          <t>Exercícios P2.pdf</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>07.04 Lâminas Comunicação e Sincronização</t>
+          <t>Exercícios P2</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr"/>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>09.04 Lâminas Semáforos.pdf</t>
+          <t>Lâminas CS 4244 Internet Programming Sockets Programming.pdf</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>09.04 Lâminas Semáforos</t>
+          <t>Lâminas CS 4244 Internet Programming Sockets Programming</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>12.03 Processos.pdf</t>
+          <t>Lâminas Sockets (material alternativo em PT).pdf</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>12.03 Processos</t>
+          <t>Lâminas Sockets (material alternativo em PT)</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>12.05 Lâminas Gerência de Memória.pdf</t>
+          <t>Lista Exercícios P1.pdf</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>12.05 Lâminas Gerência de Memória</t>
+          <t>Lista Exercícios P1</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>14 04 Troca de Mensagens.pdf</t>
+          <t>Lista Exercícios P1 Gabarito.pdf</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>14 04 Troca de Mensagens</t>
+          <t>Lista Exercícios P1 Gabarito</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr"/>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>14.04 Lâminas IPC.pdf</t>
+          <t>Lista Exercícios P2.pdf</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>14.04 Lâminas IPC</t>
+          <t>Lista Exercícios P2</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>14.04 Troca de Mensagens.pdf</t>
+          <t>lista1_gab.pdf</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>14.04 Troca de Mensagens</t>
+          <t>lista1 gab</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr"/>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>17.03 Chamada de Sistema.pdf</t>
+          <t>lista2.pdf</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>17.03 Chamada de Sistema</t>
+          <t>lista2</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr"/>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>19.03 Estruturas de Controle.pdf</t>
+          <t>Plano de Ensino.pdf</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>19.03 Estruturas de Controle</t>
+          <t>Plano de Ensino</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr"/>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>21.05 Lâminas Paginação.pdf</t>
+          <t>Programa.pdf</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>21.05 Lâminas Paginação</t>
+          <t>Programa</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr"/>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>23.06 Lâminas Gerência de Arquivos.pdf</t>
+          <t>Questões do ENADE sobre SISOP.pdf</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>23.06 Lâminas Gerência de Arquivos</t>
+          <t>Questões do ENADE sobre SISOP</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr"/>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>23.06 Lâminas Lâminas Armazenamento em Massa.pdf</t>
+          <t>07.04 Exemplo threads em Java.zip</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>23.06 Lâminas Lâminas Armazenamento em Massa</t>
+          <t>07.04 Exemplo threads em Java</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr"/>
@@ -1303,17 +1303,17 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>24.03 Escalonamento de Processos.pdf</t>
+          <t>Exemplo Criação de Processos no Unix Linux - filho.c</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>24.03 Escalonamento de Processos</t>
+          <t>Exemplo Criação de Processos no Unix Linux filho</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr"/>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>26.03 Algoritmos de Escalonamento.pdf</t>
+          <t>Exemplo Criação de Processos no Unix Linux - teste01.c</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>26.03 Algoritmos de Escalonamento</t>
+          <t>Exemplo Criação de Processos no Unix Linux teste01</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr"/>
@@ -1349,17 +1349,17 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>31.03 Threads.pdf</t>
+          <t>Exemplo Criação de Processos no Unix Linux - teste02.c</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>31.03 Threads</t>
+          <t>Exemplo Criação de Processos no Unix Linux teste02</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr"/>
@@ -1372,17 +1372,17 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Apresentação da Disciplina.pdf</t>
+          <t>Exemplo Criação de Processos no Unix Linux - teste03.c</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Apresentação da Disciplina</t>
+          <t>Exemplo Criação de Processos no Unix Linux teste03</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr"/>
@@ -1395,17 +1395,17 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Definição e Histórico.pdf</t>
+          <t>Exemplo threads em C - exemplo1.c</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Definição e Histórico</t>
+          <t>Exemplo threads em C exemplo1</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr"/>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Plano de Ensino.pdf</t>
+          <t>Exemplo threads em C - exemplo2.c</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Plano de Ensino</t>
+          <t>Exemplo threads em C exemplo2</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr"/>
@@ -1441,17 +1441,17 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Programa.pdf</t>
+          <t>Exemplo threads em C - exemplo3.c</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>código</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Programa</t>
+          <t>Exemplo threads em C exemplo3</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr"/>
